--- a/04_DESIGN_TABLES/DesignTable_6503.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6503.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -934,10 +934,10 @@
         <v>1.23</v>
       </c>
       <c r="C9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1</v>
+        <v>1.128</v>
       </c>
       <c r="E9" t="n">
         <v>0.88</v>
@@ -979,7 +979,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Air-Way s133 only (double-pass 11 rows)</t>
+          <t>Air-Way s133 only (double-pass 11 rows); M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1978 = 1.128 (table had 1.1) [user 2026-10-18 A19]; M5@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!O1978 = 1.550 (table had 1.52) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): M10@DRIVE 1.1 -&gt; OMi 1.128 (Items!N1978, M141) | A19 (user 2026-10-18, group 3 open): M5@DRIVE 1.52 -&gt; OMi 1.550 (Items!O1978, M142)</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6503.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6503.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -934,10 +934,10 @@
         <v>1.23</v>
       </c>
       <c r="C9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="D9" t="n">
-        <v>1.128</v>
+        <v>1.1</v>
       </c>
       <c r="E9" t="n">
         <v>0.88</v>
@@ -979,12 +979,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Air-Way s133 only (double-pass 11 rows); M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1978 = 1.128 (table had 1.1) [user 2026-10-18 A19]; M5@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!O1978 = 1.550 (table had 1.52) [user 2026-10-18 A19]</t>
+          <t>Air-Way s133 only (double-pass 11 rows); M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1978 = 1.128 (table had 1.1) [user 2026-10-18 A19]; M5@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!O1978 = 1.550 (table had 1.52) [user 2026-10-18 A19]; M5@DRIVE: Air-Way 1.52 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.55) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; M10@DRIVE: Air-Way 1.1 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.128) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): M10@DRIVE 1.1 -&gt; OMi 1.128 (Items!N1978, M141) | A19 (user 2026-10-18, group 3 open): M5@DRIVE 1.52 -&gt; OMi 1.550 (Items!O1978, M142)</t>
+          <t>A19 (user 2026-10-18, group 3 open): M10@DRIVE 1.1 -&gt; OMi 1.128 (Items!N1978, M141) | A19 (user 2026-10-18, group 3 open): M5@DRIVE 1.52 -&gt; OMi 1.550 (Items!O1978, M142) | 2026-10-20 Air-Way first: M5@DRIVE OMi/Brennan 1.55 -&gt; Air-Way 1.52 | 2026-10-20 Air-Way first: M10@DRIVE OMi/Brennan 1.128 -&gt; Air-Way 1.1</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6503.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6503.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1280,24 +1280,61 @@
           <t>6503-04-04-FG</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>6503-04-04-FG</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1/4-18 (A NPTF) x 7/16-20 (B UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-04-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-04-04 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): every size from OMi WebsitePartsInfo2026.xlsx Items row 1975 of this -FG part (Air-Way prints only the plain 6503, not used for the forged part); column reading N1 = OMi "L 1", M5 = "M 2", M10 = "M 1" (accepted by the user on 6503-08-08-FG, A19 group 3; Brennan TFA p38 letters M2 / M6 / M4); tap drill = Air-Way per size (A1); thread majors from the end libraries; cross-check Brennan TFA catalog p38 6503-04-04-FG M2 0.88 / M6 1.18 / M4 0.83 / C HEX 0.563 / Y FLATS 0.750 / B DRILL 0.172 - equal or rounding (same manufacturer, one source); no $PRP@DimSource column in this table - source = OMI</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 1975 (+ A1 tap drill); Brennan TFA p38 6503-04-04-FG M2 0.88 / M6 1.18 / M4 0.83 / C HEX 0.563 / Y FLATS 0.750 / B DRILL 0.172 - equal or rounding</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1354,24 +1391,61 @@
           <t>6503-12-12-FG</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.298</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>6503-12-12-FG</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>3/4-14 (A NPTF) x 1 1/16-12 (B UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-12-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): every size from OMi WebsitePartsInfo2026.xlsx Items row 1980 of this -FG part (Air-Way prints only the plain 6503, not used for the forged part); column reading N1 = OMi "L 1", M5 = "M 2", M10 = "M 1" (accepted by the user on 6503-08-08-FG, A19 group 3; Brennan TFA p38 letters M2 / M6 / M4); tap drill = Air-Way per size (A1); thread majors from the end libraries; cross-check Brennan TFA catalog p38 6503-12-12-FG M2 1.360 / M6 1.860 / M4 1.300 / C HEX 1.250 / Y FLATS 1.312 / B DRILL 0.609 - equal or rounding (same manufacturer, one source); no $PRP@DimSource column in this table - source = OMI</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 1980 (+ A1 tap drill); Brennan TFA p38 6503-12-12-FG M2 1.360 / M6 1.860 / M4 1.300 / C HEX 1.250 / Y FLATS 1.312 / B DRILL 0.609 - equal or rounding</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
